--- a/synuclein_inclusion_biogenesis_2024/image_analysis/C12_pulse_chase/3K_New_Analysis/12225_SUMMARY_important_columns.xlsx
+++ b/synuclein_inclusion_biogenesis_2024/image_analysis/C12_pulse_chase/3K_New_Analysis/12225_SUMMARY_important_columns.xlsx
@@ -468,7 +468,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -493,7 +493,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -518,7 +518,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -543,7 +543,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -568,7 +568,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -593,7 +593,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -618,7 +618,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -643,7 +643,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -668,7 +668,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -693,7 +693,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -718,7 +718,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -743,7 +743,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -768,7 +768,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -793,7 +793,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -818,7 +818,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -843,7 +843,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -868,7 +868,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -893,7 +893,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -918,7 +918,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -943,7 +943,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -968,7 +968,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -993,7 +993,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1018,7 +1018,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1043,7 +1043,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1068,7 +1068,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1093,7 +1093,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1118,7 +1118,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -1143,7 +1143,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1168,7 +1168,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1193,7 +1193,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1218,7 +1218,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -1243,7 +1243,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1268,7 +1268,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -1293,7 +1293,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1318,7 +1318,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -1343,7 +1343,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1368,7 +1368,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -1393,7 +1393,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -1418,7 +1418,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -1443,7 +1443,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -1468,7 +1468,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -1493,7 +1493,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -1518,7 +1518,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -1543,7 +1543,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -1568,7 +1568,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -1593,7 +1593,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -1618,7 +1618,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -1643,7 +1643,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -1668,7 +1668,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -1693,7 +1693,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -1718,7 +1718,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -1743,7 +1743,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -1768,7 +1768,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_03.czi</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -1793,7 +1793,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_03.czi</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -1818,7 +1818,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_03.czi</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -1843,7 +1843,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_03.czi</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -1868,7 +1868,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_03.czi</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -1893,7 +1893,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_03.czi</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -1918,7 +1918,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_03.czi</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -1943,7 +1943,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_03.czi</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -1968,7 +1968,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_03.czi</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -1993,7 +1993,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_03.czi</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -2018,7 +2018,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_03.czi</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -2043,7 +2043,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_03.czi</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -2068,7 +2068,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_03.czi</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -2093,7 +2093,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_03.czi</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -2118,7 +2118,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_03.czi</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -2143,7 +2143,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_03.czi</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -2168,7 +2168,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_03.czi</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -2193,7 +2193,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_03.czi</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -2218,7 +2218,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_03.czi</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -2243,7 +2243,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_03.czi</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -2268,7 +2268,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_03.czi</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -2293,7 +2293,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_03.czi</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -2318,7 +2318,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_03.czi</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -2343,7 +2343,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_03.czi</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -2368,7 +2368,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -2393,7 +2393,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -2418,7 +2418,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -2443,7 +2443,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -2468,7 +2468,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -2493,7 +2493,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -2518,7 +2518,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -2543,7 +2543,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -2568,7 +2568,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -2593,7 +2593,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -2618,7 +2618,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -2643,7 +2643,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -2668,7 +2668,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -2693,7 +2693,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -2718,7 +2718,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -2743,7 +2743,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -2768,7 +2768,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -2793,7 +2793,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -2818,7 +2818,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -2843,7 +2843,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -2868,7 +2868,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -2893,7 +2893,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -2918,7 +2918,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -2943,7 +2943,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -2968,7 +2968,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_06.czi</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -2993,7 +2993,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_06.czi</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -3018,7 +3018,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_06.czi</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -3043,7 +3043,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_06.czi</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -3068,7 +3068,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_06.czi</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -3093,7 +3093,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_06.czi</t>
         </is>
       </c>
       <c r="B107" t="n">
@@ -3118,7 +3118,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_06.czi</t>
         </is>
       </c>
       <c r="B108" t="n">
@@ -3143,7 +3143,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_06.czi</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -3168,7 +3168,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_06.czi</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -3193,7 +3193,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_06.czi</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -3218,7 +3218,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_06.czi</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -3243,7 +3243,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_06.czi</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -3268,7 +3268,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_24h_LT_06.czi</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -3293,7 +3293,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_01.czi</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -3318,7 +3318,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_01.czi</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -3343,7 +3343,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_01.czi</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -3368,7 +3368,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_01.czi</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -3393,7 +3393,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_01.czi</t>
         </is>
       </c>
       <c r="B119" t="n">
@@ -3418,7 +3418,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_01.czi</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -3443,7 +3443,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_01.czi</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -3468,7 +3468,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_01.czi</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -3493,7 +3493,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_01.czi</t>
         </is>
       </c>
       <c r="B123" t="n">
@@ -3518,7 +3518,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_01.czi</t>
         </is>
       </c>
       <c r="B124" t="n">
@@ -3543,7 +3543,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_01.czi</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -3568,7 +3568,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_01.czi</t>
         </is>
       </c>
       <c r="B126" t="n">
@@ -3593,7 +3593,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_01.czi</t>
         </is>
       </c>
       <c r="B127" t="n">
@@ -3618,7 +3618,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_01.czi</t>
         </is>
       </c>
       <c r="B128" t="n">
@@ -3643,7 +3643,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_01.czi</t>
         </is>
       </c>
       <c r="B129" t="n">
@@ -3668,7 +3668,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_01.czi</t>
         </is>
       </c>
       <c r="B130" t="n">
@@ -3693,7 +3693,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_01.czi</t>
         </is>
       </c>
       <c r="B131" t="n">
@@ -3718,7 +3718,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_01.czi</t>
         </is>
       </c>
       <c r="B132" t="n">
@@ -3743,7 +3743,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_01.czi</t>
         </is>
       </c>
       <c r="B133" t="n">
@@ -3768,7 +3768,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_01.czi</t>
         </is>
       </c>
       <c r="B134" t="n">
@@ -3793,7 +3793,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_02.czi</t>
         </is>
       </c>
       <c r="B135" t="n">
@@ -3818,7 +3818,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_02.czi</t>
         </is>
       </c>
       <c r="B136" t="n">
@@ -3843,7 +3843,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_02.czi</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -3868,7 +3868,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_02.czi</t>
         </is>
       </c>
       <c r="B138" t="n">
@@ -3893,7 +3893,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_02.czi</t>
         </is>
       </c>
       <c r="B139" t="n">
@@ -3918,7 +3918,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_02.czi</t>
         </is>
       </c>
       <c r="B140" t="n">
@@ -3943,7 +3943,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_02.czi</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -3968,7 +3968,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_02.czi</t>
         </is>
       </c>
       <c r="B142" t="n">
@@ -3993,7 +3993,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_03.czi</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -4018,7 +4018,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_03.czi</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -4043,7 +4043,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_03.czi</t>
         </is>
       </c>
       <c r="B145" t="n">
@@ -4068,7 +4068,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_03.czi</t>
         </is>
       </c>
       <c r="B146" t="n">
@@ -4093,7 +4093,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_03.czi</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -4118,7 +4118,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_03.czi</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -4143,7 +4143,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_03.czi</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -4168,7 +4168,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_03.czi</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -4193,7 +4193,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_03.czi</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -4218,7 +4218,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_03.czi</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -4243,7 +4243,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_03.czi</t>
         </is>
       </c>
       <c r="B153" t="n">
@@ -4268,7 +4268,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_03.czi</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -4293,7 +4293,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_03.czi</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -4318,7 +4318,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_03.czi</t>
         </is>
       </c>
       <c r="B156" t="n">
@@ -4343,7 +4343,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_03.czi</t>
         </is>
       </c>
       <c r="B157" t="n">
@@ -4368,7 +4368,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_03.czi</t>
         </is>
       </c>
       <c r="B158" t="n">
@@ -4393,7 +4393,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_03.czi</t>
         </is>
       </c>
       <c r="B159" t="n">
@@ -4418,7 +4418,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_03.czi</t>
         </is>
       </c>
       <c r="B160" t="n">
@@ -4443,7 +4443,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_03.czi</t>
         </is>
       </c>
       <c r="B161" t="n">
@@ -4468,7 +4468,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_03.czi</t>
         </is>
       </c>
       <c r="B162" t="n">
@@ -4493,7 +4493,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_03.czi</t>
         </is>
       </c>
       <c r="B163" t="n">
@@ -4518,7 +4518,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_03.czi</t>
         </is>
       </c>
       <c r="B164" t="n">
@@ -4543,7 +4543,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_03.czi</t>
         </is>
       </c>
       <c r="B165" t="n">
@@ -4568,7 +4568,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_03.czi</t>
         </is>
       </c>
       <c r="B166" t="n">
@@ -4593,7 +4593,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_04.czi</t>
         </is>
       </c>
       <c r="B167" t="n">
@@ -4618,7 +4618,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_04.czi</t>
         </is>
       </c>
       <c r="B168" t="n">
@@ -4643,7 +4643,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_04.czi</t>
         </is>
       </c>
       <c r="B169" t="n">
@@ -4668,7 +4668,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_04.czi</t>
         </is>
       </c>
       <c r="B170" t="n">
@@ -4693,7 +4693,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_04.czi</t>
         </is>
       </c>
       <c r="B171" t="n">
@@ -4718,7 +4718,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_04.czi</t>
         </is>
       </c>
       <c r="B172" t="n">
@@ -4743,7 +4743,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_04.czi</t>
         </is>
       </c>
       <c r="B173" t="n">
@@ -4768,7 +4768,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_04.czi</t>
         </is>
       </c>
       <c r="B174" t="n">
@@ -4793,7 +4793,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_04.czi</t>
         </is>
       </c>
       <c r="B175" t="n">
@@ -4818,7 +4818,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_04.czi</t>
         </is>
       </c>
       <c r="B176" t="n">
@@ -4843,7 +4843,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_04.czi</t>
         </is>
       </c>
       <c r="B177" t="n">
@@ -4868,7 +4868,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_04.czi</t>
         </is>
       </c>
       <c r="B178" t="n">
@@ -4893,7 +4893,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_04.czi</t>
         </is>
       </c>
       <c r="B179" t="n">
@@ -4918,7 +4918,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_04.czi</t>
         </is>
       </c>
       <c r="B180" t="n">
@@ -4943,7 +4943,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_04.czi</t>
         </is>
       </c>
       <c r="B181" t="n">
@@ -4968,7 +4968,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_04.czi</t>
         </is>
       </c>
       <c r="B182" t="n">
@@ -4993,7 +4993,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_04.czi</t>
         </is>
       </c>
       <c r="B183" t="n">
@@ -5018,7 +5018,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_04.czi</t>
         </is>
       </c>
       <c r="B184" t="n">
@@ -5043,7 +5043,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_04.czi</t>
         </is>
       </c>
       <c r="B185" t="n">
@@ -5068,7 +5068,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_04.czi</t>
         </is>
       </c>
       <c r="B186" t="n">
@@ -5093,7 +5093,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_04.czi</t>
         </is>
       </c>
       <c r="B187" t="n">
@@ -5118,7 +5118,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_04.czi</t>
         </is>
       </c>
       <c r="B188" t="n">
@@ -5143,7 +5143,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_04.czi</t>
         </is>
       </c>
       <c r="B189" t="n">
@@ -5168,7 +5168,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_04.czi</t>
         </is>
       </c>
       <c r="B190" t="n">
@@ -5193,7 +5193,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_04.czi</t>
         </is>
       </c>
       <c r="B191" t="n">
@@ -5218,7 +5218,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_04.czi</t>
         </is>
       </c>
       <c r="B192" t="n">
@@ -5243,7 +5243,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_04.czi</t>
         </is>
       </c>
       <c r="B193" t="n">
@@ -5268,7 +5268,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_05.czi</t>
         </is>
       </c>
       <c r="B194" t="n">
@@ -5293,7 +5293,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_05.czi</t>
         </is>
       </c>
       <c r="B195" t="n">
@@ -5318,7 +5318,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_05.czi</t>
         </is>
       </c>
       <c r="B196" t="n">
@@ -5343,7 +5343,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_05.czi</t>
         </is>
       </c>
       <c r="B197" t="n">
@@ -5368,7 +5368,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_05.czi</t>
         </is>
       </c>
       <c r="B198" t="n">
@@ -5393,7 +5393,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_05.czi</t>
         </is>
       </c>
       <c r="B199" t="n">
@@ -5418,7 +5418,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_05.czi</t>
         </is>
       </c>
       <c r="B200" t="n">
@@ -5443,7 +5443,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_05.czi</t>
         </is>
       </c>
       <c r="B201" t="n">
@@ -5468,7 +5468,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_05.czi</t>
         </is>
       </c>
       <c r="B202" t="n">
@@ -5493,7 +5493,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_05.czi</t>
         </is>
       </c>
       <c r="B203" t="n">
@@ -5518,7 +5518,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_05.czi</t>
         </is>
       </c>
       <c r="B204" t="n">
@@ -5543,7 +5543,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_05.czi</t>
         </is>
       </c>
       <c r="B205" t="n">
@@ -5568,7 +5568,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_05.czi</t>
         </is>
       </c>
       <c r="B206" t="n">
@@ -5593,7 +5593,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_05.czi</t>
         </is>
       </c>
       <c r="B207" t="n">
@@ -5618,7 +5618,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_05.czi</t>
         </is>
       </c>
       <c r="B208" t="n">
@@ -5643,7 +5643,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_05.czi</t>
         </is>
       </c>
       <c r="B209" t="n">
@@ -5668,7 +5668,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_05.czi</t>
         </is>
       </c>
       <c r="B210" t="n">
@@ -5693,7 +5693,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_05.czi</t>
         </is>
       </c>
       <c r="B211" t="n">
@@ -5718,7 +5718,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_05.czi</t>
         </is>
       </c>
       <c r="B212" t="n">
@@ -5743,7 +5743,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_05.czi</t>
         </is>
       </c>
       <c r="B213" t="n">
@@ -5768,7 +5768,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_05.czi</t>
         </is>
       </c>
       <c r="B214" t="n">
@@ -5793,7 +5793,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_05.czi</t>
         </is>
       </c>
       <c r="B215" t="n">
@@ -5818,7 +5818,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_05.czi</t>
         </is>
       </c>
       <c r="B216" t="n">
@@ -5843,7 +5843,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_05.czi</t>
         </is>
       </c>
       <c r="B217" t="n">
@@ -5868,7 +5868,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_05.czi</t>
         </is>
       </c>
       <c r="B218" t="n">
@@ -5893,7 +5893,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_05.czi</t>
         </is>
       </c>
       <c r="B219" t="n">
@@ -5918,7 +5918,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_05.czi</t>
         </is>
       </c>
       <c r="B220" t="n">
@@ -5943,7 +5943,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_05.czi</t>
         </is>
       </c>
       <c r="B221" t="n">
@@ -5968,7 +5968,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_05.czi</t>
         </is>
       </c>
       <c r="B222" t="n">
@@ -5993,7 +5993,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_05.czi</t>
         </is>
       </c>
       <c r="B223" t="n">
@@ -6018,7 +6018,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_05.czi</t>
         </is>
       </c>
       <c r="B224" t="n">
@@ -6043,7 +6043,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_05.czi</t>
         </is>
       </c>
       <c r="B225" t="n">
@@ -6068,7 +6068,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_05.czi</t>
         </is>
       </c>
       <c r="B226" t="n">
@@ -6093,7 +6093,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_05.czi</t>
         </is>
       </c>
       <c r="B227" t="n">
@@ -6118,7 +6118,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_05.czi</t>
         </is>
       </c>
       <c r="B228" t="n">
@@ -6143,7 +6143,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_05.czi</t>
         </is>
       </c>
       <c r="B229" t="n">
@@ -6168,7 +6168,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_06.czi</t>
         </is>
       </c>
       <c r="B230" t="n">
@@ -6193,7 +6193,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_06.czi</t>
         </is>
       </c>
       <c r="B231" t="n">
@@ -6218,7 +6218,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_06.czi</t>
         </is>
       </c>
       <c r="B232" t="n">
@@ -6243,7 +6243,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_06.czi</t>
         </is>
       </c>
       <c r="B233" t="n">
@@ -6268,7 +6268,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_06.czi</t>
         </is>
       </c>
       <c r="B234" t="n">
@@ -6293,7 +6293,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_06.czi</t>
         </is>
       </c>
       <c r="B235" t="n">
@@ -6318,7 +6318,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_06.czi</t>
         </is>
       </c>
       <c r="B236" t="n">
@@ -6343,7 +6343,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_06.czi</t>
         </is>
       </c>
       <c r="B237" t="n">
@@ -6368,7 +6368,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_06.czi</t>
         </is>
       </c>
       <c r="B238" t="n">
@@ -6393,7 +6393,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_06.czi</t>
         </is>
       </c>
       <c r="B239" t="n">
@@ -6418,7 +6418,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_06.czi</t>
         </is>
       </c>
       <c r="B240" t="n">
@@ -6443,7 +6443,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_06.czi</t>
         </is>
       </c>
       <c r="B241" t="n">
@@ -6468,7 +6468,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_06.czi</t>
         </is>
       </c>
       <c r="B242" t="n">
@@ -6493,7 +6493,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_06.czi</t>
         </is>
       </c>
       <c r="B243" t="n">
@@ -6518,7 +6518,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_06.czi</t>
         </is>
       </c>
       <c r="B244" t="n">
@@ -6543,7 +6543,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_06.czi</t>
         </is>
       </c>
       <c r="B245" t="n">
@@ -6568,7 +6568,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_06.czi</t>
         </is>
       </c>
       <c r="B246" t="n">
@@ -6593,7 +6593,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_06.czi</t>
         </is>
       </c>
       <c r="B247" t="n">
@@ -6618,7 +6618,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_06.czi</t>
         </is>
       </c>
       <c r="B248" t="n">
@@ -6643,7 +6643,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_06.czi</t>
         </is>
       </c>
       <c r="B249" t="n">
@@ -6668,7 +6668,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_06.czi</t>
         </is>
       </c>
       <c r="B250" t="n">
@@ -6693,7 +6693,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_06.czi</t>
         </is>
       </c>
       <c r="B251" t="n">
@@ -6718,7 +6718,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_06.czi</t>
         </is>
       </c>
       <c r="B252" t="n">
@@ -6743,7 +6743,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_06.czi</t>
         </is>
       </c>
       <c r="B253" t="n">
@@ -6768,7 +6768,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_06.czi</t>
         </is>
       </c>
       <c r="B254" t="n">
@@ -6793,7 +6793,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_06.czi</t>
         </is>
       </c>
       <c r="B255" t="n">
@@ -6818,7 +6818,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_06.czi</t>
         </is>
       </c>
       <c r="B256" t="n">
@@ -6843,7 +6843,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_06.czi</t>
         </is>
       </c>
       <c r="B257" t="n">
@@ -6868,7 +6868,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_06.czi</t>
         </is>
       </c>
       <c r="B258" t="n">
@@ -6893,7 +6893,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_06.czi</t>
         </is>
       </c>
       <c r="B259" t="n">
@@ -6918,7 +6918,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_06.czi</t>
         </is>
       </c>
       <c r="B260" t="n">
@@ -6943,7 +6943,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_06.czi</t>
         </is>
       </c>
       <c r="B261" t="n">
@@ -6968,7 +6968,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_06.czi</t>
         </is>
       </c>
       <c r="B262" t="n">
@@ -6993,7 +6993,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_06.czi</t>
         </is>
       </c>
       <c r="B263" t="n">
@@ -7018,7 +7018,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_06.czi</t>
         </is>
       </c>
       <c r="B264" t="n">
@@ -7043,7 +7043,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_06.czi</t>
         </is>
       </c>
       <c r="B265" t="n">
@@ -7068,7 +7068,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_06.czi</t>
         </is>
       </c>
       <c r="B266" t="n">
@@ -7093,7 +7093,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_06.czi</t>
         </is>
       </c>
       <c r="B267" t="n">
@@ -7118,7 +7118,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_06.czi</t>
         </is>
       </c>
       <c r="B268" t="n">
@@ -7143,7 +7143,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_06.czi</t>
         </is>
       </c>
       <c r="B269" t="n">
@@ -7168,7 +7168,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_06.czi</t>
         </is>
       </c>
       <c r="B270" t="n">
@@ -7193,7 +7193,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_DMEM_6h_LT_06.czi</t>
         </is>
       </c>
       <c r="B271" t="n">
@@ -7218,7 +7218,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B272" t="n">
@@ -7243,7 +7243,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B273" t="n">
@@ -7268,7 +7268,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B274" t="n">
@@ -7293,7 +7293,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B275" t="n">
@@ -7318,7 +7318,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B276" t="n">
@@ -7343,7 +7343,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B277" t="n">
@@ -7368,7 +7368,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B278" t="n">
@@ -7393,7 +7393,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B279" t="n">
@@ -7418,7 +7418,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B280" t="n">
@@ -7443,7 +7443,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B281" t="n">
@@ -7468,7 +7468,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B282" t="n">
@@ -7493,7 +7493,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B283" t="n">
@@ -7518,7 +7518,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B284" t="n">
@@ -7543,7 +7543,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B285" t="n">
@@ -7568,7 +7568,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B286" t="n">
@@ -7593,7 +7593,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B287" t="n">
@@ -7618,7 +7618,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B288" t="n">
@@ -7643,7 +7643,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B289" t="n">
@@ -7668,7 +7668,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B290" t="n">
@@ -7693,7 +7693,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B291" t="n">
@@ -7718,7 +7718,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B292" t="n">
@@ -7743,7 +7743,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B293" t="n">
@@ -7768,7 +7768,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B294" t="n">
@@ -7793,7 +7793,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B295" t="n">
@@ -7818,7 +7818,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B296" t="n">
@@ -7843,7 +7843,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B297" t="n">
@@ -7868,7 +7868,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B298" t="n">
@@ -7893,7 +7893,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B299" t="n">
@@ -7918,7 +7918,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B300" t="n">
@@ -7943,7 +7943,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B301" t="n">
@@ -7968,7 +7968,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B302" t="n">
@@ -7993,7 +7993,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B303" t="n">
@@ -8018,7 +8018,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B304" t="n">
@@ -8043,7 +8043,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B305" t="n">
@@ -8068,7 +8068,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B306" t="n">
@@ -8093,7 +8093,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B307" t="n">
@@ -8118,7 +8118,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B308" t="n">
@@ -8143,7 +8143,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B309" t="n">
@@ -8168,7 +8168,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B310" t="n">
@@ -8193,7 +8193,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B311" t="n">
@@ -8218,7 +8218,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B312" t="n">
@@ -8243,7 +8243,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B313" t="n">
@@ -8268,7 +8268,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_03.czi</t>
         </is>
       </c>
       <c r="B314" t="n">
@@ -8293,7 +8293,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_03.czi</t>
         </is>
       </c>
       <c r="B315" t="n">
@@ -8318,7 +8318,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_03.czi</t>
         </is>
       </c>
       <c r="B316" t="n">
@@ -8343,7 +8343,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_03.czi</t>
         </is>
       </c>
       <c r="B317" t="n">
@@ -8368,7 +8368,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_03.czi</t>
         </is>
       </c>
       <c r="B318" t="n">
@@ -8393,7 +8393,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_03.czi</t>
         </is>
       </c>
       <c r="B319" t="n">
@@ -8418,7 +8418,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_03.czi</t>
         </is>
       </c>
       <c r="B320" t="n">
@@ -8443,7 +8443,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_03.czi</t>
         </is>
       </c>
       <c r="B321" t="n">
@@ -8468,7 +8468,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_03.czi</t>
         </is>
       </c>
       <c r="B322" t="n">
@@ -8493,7 +8493,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_03.czi</t>
         </is>
       </c>
       <c r="B323" t="n">
@@ -8518,7 +8518,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_03.czi</t>
         </is>
       </c>
       <c r="B324" t="n">
@@ -8543,7 +8543,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_03.czi</t>
         </is>
       </c>
       <c r="B325" t="n">
@@ -8568,7 +8568,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_03.czi</t>
         </is>
       </c>
       <c r="B326" t="n">
@@ -8593,7 +8593,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_03.czi</t>
         </is>
       </c>
       <c r="B327" t="n">
@@ -8618,7 +8618,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_03.czi</t>
         </is>
       </c>
       <c r="B328" t="n">
@@ -8643,7 +8643,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_03.czi</t>
         </is>
       </c>
       <c r="B329" t="n">
@@ -8668,7 +8668,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_03.czi</t>
         </is>
       </c>
       <c r="B330" t="n">
@@ -8693,7 +8693,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_03.czi</t>
         </is>
       </c>
       <c r="B331" t="n">
@@ -8718,7 +8718,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_03.czi</t>
         </is>
       </c>
       <c r="B332" t="n">
@@ -8743,7 +8743,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_04.czi</t>
         </is>
       </c>
       <c r="B333" t="n">
@@ -8768,7 +8768,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_04.czi</t>
         </is>
       </c>
       <c r="B334" t="n">
@@ -8793,7 +8793,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_04.czi</t>
         </is>
       </c>
       <c r="B335" t="n">
@@ -8818,7 +8818,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_04.czi</t>
         </is>
       </c>
       <c r="B336" t="n">
@@ -8843,7 +8843,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_04.czi</t>
         </is>
       </c>
       <c r="B337" t="n">
@@ -8868,7 +8868,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_04.czi</t>
         </is>
       </c>
       <c r="B338" t="n">
@@ -8893,7 +8893,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_04.czi</t>
         </is>
       </c>
       <c r="B339" t="n">
@@ -8918,7 +8918,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_04.czi</t>
         </is>
       </c>
       <c r="B340" t="n">
@@ -8943,7 +8943,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_04.czi</t>
         </is>
       </c>
       <c r="B341" t="n">
@@ -8968,7 +8968,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_04.czi</t>
         </is>
       </c>
       <c r="B342" t="n">
@@ -8993,7 +8993,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_04.czi</t>
         </is>
       </c>
       <c r="B343" t="n">
@@ -9018,7 +9018,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_04.czi</t>
         </is>
       </c>
       <c r="B344" t="n">
@@ -9043,7 +9043,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_04.czi</t>
         </is>
       </c>
       <c r="B345" t="n">
@@ -9068,7 +9068,7 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_04.czi</t>
         </is>
       </c>
       <c r="B346" t="n">
@@ -9093,7 +9093,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_04.czi</t>
         </is>
       </c>
       <c r="B347" t="n">
@@ -9118,7 +9118,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_04.czi</t>
         </is>
       </c>
       <c r="B348" t="n">
@@ -9143,7 +9143,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_04.czi</t>
         </is>
       </c>
       <c r="B349" t="n">
@@ -9168,7 +9168,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B350" t="n">
@@ -9193,7 +9193,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B351" t="n">
@@ -9218,7 +9218,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B352" t="n">
@@ -9243,7 +9243,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B353" t="n">
@@ -9268,7 +9268,7 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B354" t="n">
@@ -9293,7 +9293,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B355" t="n">
@@ -9318,7 +9318,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B356" t="n">
@@ -9343,7 +9343,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B357" t="n">
@@ -9368,7 +9368,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B358" t="n">
@@ -9393,7 +9393,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B359" t="n">
@@ -9418,7 +9418,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B360" t="n">
@@ -9443,7 +9443,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B361" t="n">
@@ -9468,7 +9468,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B362" t="n">
@@ -9493,7 +9493,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B363" t="n">
@@ -9518,7 +9518,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B364" t="n">
@@ -9543,7 +9543,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B365" t="n">
@@ -9568,7 +9568,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B366" t="n">
@@ -9593,7 +9593,7 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B367" t="n">
@@ -9618,7 +9618,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B368" t="n">
@@ -9643,7 +9643,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B369" t="n">
@@ -9668,7 +9668,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_06.czi</t>
         </is>
       </c>
       <c r="B370" t="n">
@@ -9693,7 +9693,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_06.czi</t>
         </is>
       </c>
       <c r="B371" t="n">
@@ -9718,7 +9718,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_06.czi</t>
         </is>
       </c>
       <c r="B372" t="n">
@@ -9743,7 +9743,7 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_06.czi</t>
         </is>
       </c>
       <c r="B373" t="n">
@@ -9768,7 +9768,7 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_06.czi</t>
         </is>
       </c>
       <c r="B374" t="n">
@@ -9793,7 +9793,7 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_06.czi</t>
         </is>
       </c>
       <c r="B375" t="n">
@@ -9818,7 +9818,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_06.czi</t>
         </is>
       </c>
       <c r="B376" t="n">
@@ -9843,7 +9843,7 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_06.czi</t>
         </is>
       </c>
       <c r="B377" t="n">
@@ -9868,7 +9868,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_06.czi</t>
         </is>
       </c>
       <c r="B378" t="n">
@@ -9893,7 +9893,7 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_06.czi</t>
         </is>
       </c>
       <c r="B379" t="n">
@@ -9918,7 +9918,7 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_06.czi</t>
         </is>
       </c>
       <c r="B380" t="n">
@@ -9943,7 +9943,7 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_06.czi</t>
         </is>
       </c>
       <c r="B381" t="n">
@@ -9968,7 +9968,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_06.czi</t>
         </is>
       </c>
       <c r="B382" t="n">
@@ -9993,7 +9993,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_06.czi</t>
         </is>
       </c>
       <c r="B383" t="n">
@@ -10018,7 +10018,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_24h_LT_06.czi</t>
         </is>
       </c>
       <c r="B384" t="n">
@@ -10043,7 +10043,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_01.czi</t>
         </is>
       </c>
       <c r="B385" t="n">
@@ -10068,7 +10068,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_01.czi</t>
         </is>
       </c>
       <c r="B386" t="n">
@@ -10093,7 +10093,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_01.czi</t>
         </is>
       </c>
       <c r="B387" t="n">
@@ -10118,7 +10118,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_01.czi</t>
         </is>
       </c>
       <c r="B388" t="n">
@@ -10143,7 +10143,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_01.czi</t>
         </is>
       </c>
       <c r="B389" t="n">
@@ -10168,7 +10168,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_01.czi</t>
         </is>
       </c>
       <c r="B390" t="n">
@@ -10193,7 +10193,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_01.czi</t>
         </is>
       </c>
       <c r="B391" t="n">
@@ -10218,7 +10218,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_01.czi</t>
         </is>
       </c>
       <c r="B392" t="n">
@@ -10243,7 +10243,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_01.czi</t>
         </is>
       </c>
       <c r="B393" t="n">
@@ -10268,7 +10268,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_01.czi</t>
         </is>
       </c>
       <c r="B394" t="n">
@@ -10293,7 +10293,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_01.czi</t>
         </is>
       </c>
       <c r="B395" t="n">
@@ -10318,7 +10318,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_01.czi</t>
         </is>
       </c>
       <c r="B396" t="n">
@@ -10343,7 +10343,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_01.czi</t>
         </is>
       </c>
       <c r="B397" t="n">
@@ -10368,7 +10368,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_01.czi</t>
         </is>
       </c>
       <c r="B398" t="n">
@@ -10393,7 +10393,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_01.czi</t>
         </is>
       </c>
       <c r="B399" t="n">
@@ -10418,7 +10418,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_01.czi</t>
         </is>
       </c>
       <c r="B400" t="n">
@@ -10443,7 +10443,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_01.czi</t>
         </is>
       </c>
       <c r="B401" t="n">
@@ -10468,7 +10468,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_01.czi</t>
         </is>
       </c>
       <c r="B402" t="n">
@@ -10493,7 +10493,7 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_01.czi</t>
         </is>
       </c>
       <c r="B403" t="n">
@@ -10518,7 +10518,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_01.czi</t>
         </is>
       </c>
       <c r="B404" t="n">
@@ -10543,7 +10543,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_01.czi</t>
         </is>
       </c>
       <c r="B405" t="n">
@@ -10568,7 +10568,7 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_01.czi</t>
         </is>
       </c>
       <c r="B406" t="n">
@@ -10593,7 +10593,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_01.czi</t>
         </is>
       </c>
       <c r="B407" t="n">
@@ -10618,7 +10618,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_01.czi</t>
         </is>
       </c>
       <c r="B408" t="n">
@@ -10643,7 +10643,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_02.czi</t>
         </is>
       </c>
       <c r="B409" t="n">
@@ -10668,7 +10668,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_02.czi</t>
         </is>
       </c>
       <c r="B410" t="n">
@@ -10693,7 +10693,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_02.czi</t>
         </is>
       </c>
       <c r="B411" t="n">
@@ -10718,7 +10718,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_02.czi</t>
         </is>
       </c>
       <c r="B412" t="n">
@@ -10743,7 +10743,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_02.czi</t>
         </is>
       </c>
       <c r="B413" t="n">
@@ -10768,7 +10768,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_02.czi</t>
         </is>
       </c>
       <c r="B414" t="n">
@@ -10793,7 +10793,7 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_02.czi</t>
         </is>
       </c>
       <c r="B415" t="n">
@@ -10818,7 +10818,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_02.czi</t>
         </is>
       </c>
       <c r="B416" t="n">
@@ -10843,7 +10843,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_02.czi</t>
         </is>
       </c>
       <c r="B417" t="n">
@@ -10868,7 +10868,7 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_02.czi</t>
         </is>
       </c>
       <c r="B418" t="n">
@@ -10893,7 +10893,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_02.czi</t>
         </is>
       </c>
       <c r="B419" t="n">
@@ -10918,7 +10918,7 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_02.czi</t>
         </is>
       </c>
       <c r="B420" t="n">
@@ -10943,7 +10943,7 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_02.czi</t>
         </is>
       </c>
       <c r="B421" t="n">
@@ -10968,7 +10968,7 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_02.czi</t>
         </is>
       </c>
       <c r="B422" t="n">
@@ -10993,7 +10993,7 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_02.czi</t>
         </is>
       </c>
       <c r="B423" t="n">
@@ -11018,7 +11018,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_02.czi</t>
         </is>
       </c>
       <c r="B424" t="n">
@@ -11043,7 +11043,7 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_02.czi</t>
         </is>
       </c>
       <c r="B425" t="n">
@@ -11068,7 +11068,7 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_02.czi</t>
         </is>
       </c>
       <c r="B426" t="n">
@@ -11093,7 +11093,7 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_02.czi</t>
         </is>
       </c>
       <c r="B427" t="n">
@@ -11118,7 +11118,7 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_02.czi</t>
         </is>
       </c>
       <c r="B428" t="n">
@@ -11143,7 +11143,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_02.czi</t>
         </is>
       </c>
       <c r="B429" t="n">
@@ -11168,7 +11168,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_02.czi</t>
         </is>
       </c>
       <c r="B430" t="n">
@@ -11193,7 +11193,7 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_02.czi</t>
         </is>
       </c>
       <c r="B431" t="n">
@@ -11218,7 +11218,7 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_02.czi</t>
         </is>
       </c>
       <c r="B432" t="n">
@@ -11243,7 +11243,7 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_02.czi</t>
         </is>
       </c>
       <c r="B433" t="n">
@@ -11268,7 +11268,7 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_02.czi</t>
         </is>
       </c>
       <c r="B434" t="n">
@@ -11293,7 +11293,7 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_02.czi</t>
         </is>
       </c>
       <c r="B435" t="n">
@@ -11318,7 +11318,7 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_02.czi</t>
         </is>
       </c>
       <c r="B436" t="n">
@@ -11343,7 +11343,7 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_02.czi</t>
         </is>
       </c>
       <c r="B437" t="n">
@@ -11368,7 +11368,7 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_02.czi</t>
         </is>
       </c>
       <c r="B438" t="n">
@@ -11393,7 +11393,7 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_02.czi</t>
         </is>
       </c>
       <c r="B439" t="n">
@@ -11418,7 +11418,7 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_02.czi</t>
         </is>
       </c>
       <c r="B440" t="n">
@@ -11443,7 +11443,7 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_04.czi</t>
         </is>
       </c>
       <c r="B441" t="n">
@@ -11468,7 +11468,7 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_04.czi</t>
         </is>
       </c>
       <c r="B442" t="n">
@@ -11493,7 +11493,7 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_04.czi</t>
         </is>
       </c>
       <c r="B443" t="n">
@@ -11518,7 +11518,7 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_04.czi</t>
         </is>
       </c>
       <c r="B444" t="n">
@@ -11543,7 +11543,7 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_04.czi</t>
         </is>
       </c>
       <c r="B445" t="n">
@@ -11568,7 +11568,7 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_04.czi</t>
         </is>
       </c>
       <c r="B446" t="n">
@@ -11593,7 +11593,7 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_04.czi</t>
         </is>
       </c>
       <c r="B447" t="n">
@@ -11618,7 +11618,7 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_04.czi</t>
         </is>
       </c>
       <c r="B448" t="n">
@@ -11643,7 +11643,7 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_04.czi</t>
         </is>
       </c>
       <c r="B449" t="n">
@@ -11668,7 +11668,7 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_04.czi</t>
         </is>
       </c>
       <c r="B450" t="n">
@@ -11693,7 +11693,7 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_04.czi</t>
         </is>
       </c>
       <c r="B451" t="n">
@@ -11718,7 +11718,7 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_04.czi</t>
         </is>
       </c>
       <c r="B452" t="n">
@@ -11743,7 +11743,7 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_04.czi</t>
         </is>
       </c>
       <c r="B453" t="n">
@@ -11768,7 +11768,7 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_04.czi</t>
         </is>
       </c>
       <c r="B454" t="n">
@@ -11793,7 +11793,7 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_04.czi</t>
         </is>
       </c>
       <c r="B455" t="n">
@@ -11818,7 +11818,7 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_04.czi</t>
         </is>
       </c>
       <c r="B456" t="n">
@@ -11843,7 +11843,7 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_04.czi</t>
         </is>
       </c>
       <c r="B457" t="n">
@@ -11868,7 +11868,7 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_04.czi</t>
         </is>
       </c>
       <c r="B458" t="n">
@@ -11893,7 +11893,7 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_04.czi</t>
         </is>
       </c>
       <c r="B459" t="n">
@@ -11918,7 +11918,7 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_04.czi</t>
         </is>
       </c>
       <c r="B460" t="n">
@@ -11943,7 +11943,7 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_04.czi</t>
         </is>
       </c>
       <c r="B461" t="n">
@@ -11968,7 +11968,7 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_04.czi</t>
         </is>
       </c>
       <c r="B462" t="n">
@@ -11993,7 +11993,7 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_04.czi</t>
         </is>
       </c>
       <c r="B463" t="n">
@@ -12018,7 +12018,7 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_04.czi</t>
         </is>
       </c>
       <c r="B464" t="n">
@@ -12043,7 +12043,7 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_04.czi</t>
         </is>
       </c>
       <c r="B465" t="n">
@@ -12068,7 +12068,7 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_04.czi</t>
         </is>
       </c>
       <c r="B466" t="n">
@@ -12093,7 +12093,7 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_04.czi</t>
         </is>
       </c>
       <c r="B467" t="n">
@@ -12118,7 +12118,7 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_04.czi</t>
         </is>
       </c>
       <c r="B468" t="n">
@@ -12143,7 +12143,7 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_04.czi</t>
         </is>
       </c>
       <c r="B469" t="n">
@@ -12168,7 +12168,7 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_04.czi</t>
         </is>
       </c>
       <c r="B470" t="n">
@@ -12193,7 +12193,7 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_05.czi</t>
         </is>
       </c>
       <c r="B471" t="n">
@@ -12218,7 +12218,7 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_05.czi</t>
         </is>
       </c>
       <c r="B472" t="n">
@@ -12243,7 +12243,7 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_05.czi</t>
         </is>
       </c>
       <c r="B473" t="n">
@@ -12268,7 +12268,7 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_05.czi</t>
         </is>
       </c>
       <c r="B474" t="n">
@@ -12293,7 +12293,7 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_05.czi</t>
         </is>
       </c>
       <c r="B475" t="n">
@@ -12318,7 +12318,7 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_05.czi</t>
         </is>
       </c>
       <c r="B476" t="n">
@@ -12343,7 +12343,7 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_05.czi</t>
         </is>
       </c>
       <c r="B477" t="n">
@@ -12368,7 +12368,7 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_05.czi</t>
         </is>
       </c>
       <c r="B478" t="n">
@@ -12393,7 +12393,7 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_05.czi</t>
         </is>
       </c>
       <c r="B479" t="n">
@@ -12418,7 +12418,7 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_05.czi</t>
         </is>
       </c>
       <c r="B480" t="n">
@@ -12443,7 +12443,7 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_05.czi</t>
         </is>
       </c>
       <c r="B481" t="n">
@@ -12468,7 +12468,7 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_05.czi</t>
         </is>
       </c>
       <c r="B482" t="n">
@@ -12493,7 +12493,7 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_05.czi</t>
         </is>
       </c>
       <c r="B483" t="n">
@@ -12518,7 +12518,7 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_05.czi</t>
         </is>
       </c>
       <c r="B484" t="n">
@@ -12543,7 +12543,7 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_05.czi</t>
         </is>
       </c>
       <c r="B485" t="n">
@@ -12568,7 +12568,7 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_05.czi</t>
         </is>
       </c>
       <c r="B486" t="n">
@@ -12593,7 +12593,7 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_05.czi</t>
         </is>
       </c>
       <c r="B487" t="n">
@@ -12618,7 +12618,7 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_05.czi</t>
         </is>
       </c>
       <c r="B488" t="n">
@@ -12643,7 +12643,7 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_05.czi</t>
         </is>
       </c>
       <c r="B489" t="n">
@@ -12668,7 +12668,7 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_05.czi</t>
         </is>
       </c>
       <c r="B490" t="n">
@@ -12693,7 +12693,7 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_05.czi</t>
         </is>
       </c>
       <c r="B491" t="n">
@@ -12718,7 +12718,7 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_05.czi</t>
         </is>
       </c>
       <c r="B492" t="n">
@@ -12743,7 +12743,7 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_05.czi</t>
         </is>
       </c>
       <c r="B493" t="n">
@@ -12768,7 +12768,7 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_05.czi</t>
         </is>
       </c>
       <c r="B494" t="n">
@@ -12793,7 +12793,7 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_05.czi</t>
         </is>
       </c>
       <c r="B495" t="n">
@@ -12818,7 +12818,7 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_06.czi</t>
         </is>
       </c>
       <c r="B496" t="n">
@@ -12843,7 +12843,7 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_06.czi</t>
         </is>
       </c>
       <c r="B497" t="n">
@@ -12868,7 +12868,7 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_06.czi</t>
         </is>
       </c>
       <c r="B498" t="n">
@@ -12893,7 +12893,7 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_06.czi</t>
         </is>
       </c>
       <c r="B499" t="n">
@@ -12918,7 +12918,7 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_06.czi</t>
         </is>
       </c>
       <c r="B500" t="n">
@@ -12943,7 +12943,7 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_06.czi</t>
         </is>
       </c>
       <c r="B501" t="n">
@@ -12968,7 +12968,7 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_06.czi</t>
         </is>
       </c>
       <c r="B502" t="n">
@@ -12993,7 +12993,7 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_06.czi</t>
         </is>
       </c>
       <c r="B503" t="n">
@@ -13018,7 +13018,7 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_06.czi</t>
         </is>
       </c>
       <c r="B504" t="n">
@@ -13043,7 +13043,7 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_06.czi</t>
         </is>
       </c>
       <c r="B505" t="n">
@@ -13068,7 +13068,7 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_06.czi</t>
         </is>
       </c>
       <c r="B506" t="n">
@@ -13093,7 +13093,7 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_06.czi</t>
         </is>
       </c>
       <c r="B507" t="n">
@@ -13118,7 +13118,7 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_06.czi</t>
         </is>
       </c>
       <c r="B508" t="n">
@@ -13143,7 +13143,7 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_06.czi</t>
         </is>
       </c>
       <c r="B509" t="n">
@@ -13168,7 +13168,7 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_06.czi</t>
         </is>
       </c>
       <c r="B510" t="n">
@@ -13193,7 +13193,7 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_06.czi</t>
         </is>
       </c>
       <c r="B511" t="n">
@@ -13218,7 +13218,7 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_06.czi</t>
         </is>
       </c>
       <c r="B512" t="n">
@@ -13243,7 +13243,7 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_06.czi</t>
         </is>
       </c>
       <c r="B513" t="n">
@@ -13268,7 +13268,7 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_06.czi</t>
         </is>
       </c>
       <c r="B514" t="n">
@@ -13293,7 +13293,7 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_06.czi</t>
         </is>
       </c>
       <c r="B515" t="n">
@@ -13318,7 +13318,7 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_06.czi</t>
         </is>
       </c>
       <c r="B516" t="n">
@@ -13343,7 +13343,7 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_06.czi</t>
         </is>
       </c>
       <c r="B517" t="n">
@@ -13368,7 +13368,7 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_06.czi</t>
         </is>
       </c>
       <c r="B518" t="n">
@@ -13393,7 +13393,7 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_06.czi</t>
         </is>
       </c>
       <c r="B519" t="n">
@@ -13418,7 +13418,7 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_06.czi</t>
         </is>
       </c>
       <c r="B520" t="n">
@@ -13443,7 +13443,7 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_06.czi</t>
         </is>
       </c>
       <c r="B521" t="n">
@@ -13468,7 +13468,7 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_06.czi</t>
         </is>
       </c>
       <c r="B522" t="n">
@@ -13493,7 +13493,7 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_06.czi</t>
         </is>
       </c>
       <c r="B523" t="n">
@@ -13518,7 +13518,7 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_06.czi</t>
         </is>
       </c>
       <c r="B524" t="n">
@@ -13543,7 +13543,7 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_06.czi</t>
         </is>
       </c>
       <c r="B525" t="n">
@@ -13568,7 +13568,7 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_06.czi</t>
         </is>
       </c>
       <c r="B526" t="n">
@@ -13593,7 +13593,7 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_06.czi</t>
         </is>
       </c>
       <c r="B527" t="n">
@@ -13618,7 +13618,7 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_06.czi</t>
         </is>
       </c>
       <c r="B528" t="n">
@@ -13643,7 +13643,7 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_06.czi</t>
         </is>
       </c>
       <c r="B529" t="n">
@@ -13668,7 +13668,7 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_06.czi</t>
         </is>
       </c>
       <c r="B530" t="n">
@@ -13693,7 +13693,7 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_06.czi</t>
         </is>
       </c>
       <c r="B531" t="n">
@@ -13718,7 +13718,7 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_06.czi</t>
         </is>
       </c>
       <c r="B532" t="n">
@@ -13743,7 +13743,7 @@
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_HBSS_6h_LT_06.czi</t>
         </is>
       </c>
       <c r="B533" t="n">
@@ -13768,7 +13768,7 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B534" t="n">
@@ -13793,7 +13793,7 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B535" t="n">
@@ -13818,7 +13818,7 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B536" t="n">
@@ -13843,7 +13843,7 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B537" t="n">
@@ -13868,7 +13868,7 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B538" t="n">
@@ -13893,7 +13893,7 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B539" t="n">
@@ -13918,7 +13918,7 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B540" t="n">
@@ -13943,7 +13943,7 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B541" t="n">
@@ -13968,7 +13968,7 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B542" t="n">
@@ -13993,7 +13993,7 @@
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B543" t="n">
@@ -14018,7 +14018,7 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B544" t="n">
@@ -14043,7 +14043,7 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B545" t="n">
@@ -14068,7 +14068,7 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B546" t="n">
@@ -14093,7 +14093,7 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B547" t="n">
@@ -14118,7 +14118,7 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B548" t="n">
@@ -14143,7 +14143,7 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B549" t="n">
@@ -14168,7 +14168,7 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B550" t="n">
@@ -14193,7 +14193,7 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B551" t="n">
@@ -14218,7 +14218,7 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B552" t="n">
@@ -14243,7 +14243,7 @@
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B553" t="n">
@@ -14268,7 +14268,7 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B554" t="n">
@@ -14293,7 +14293,7 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B555" t="n">
@@ -14318,7 +14318,7 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B556" t="n">
@@ -14343,7 +14343,7 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B557" t="n">
@@ -14368,7 +14368,7 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B558" t="n">
@@ -14393,7 +14393,7 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B559" t="n">
@@ -14418,7 +14418,7 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B560" t="n">
@@ -14443,7 +14443,7 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B561" t="n">
@@ -14468,7 +14468,7 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B562" t="n">
@@ -14493,7 +14493,7 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B563" t="n">
@@ -14518,7 +14518,7 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B564" t="n">
@@ -14543,7 +14543,7 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B565" t="n">
@@ -14568,7 +14568,7 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B566" t="n">
@@ -14593,7 +14593,7 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B567" t="n">
@@ -14618,7 +14618,7 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B568" t="n">
@@ -14643,7 +14643,7 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B569" t="n">
@@ -14668,7 +14668,7 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B570" t="n">
@@ -14693,7 +14693,7 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_01.czi</t>
         </is>
       </c>
       <c r="B571" t="n">
@@ -14718,7 +14718,7 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B572" t="n">
@@ -14743,7 +14743,7 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B573" t="n">
@@ -14768,7 +14768,7 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B574" t="n">
@@ -14793,7 +14793,7 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B575" t="n">
@@ -14818,7 +14818,7 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B576" t="n">
@@ -14843,7 +14843,7 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B577" t="n">
@@ -14868,7 +14868,7 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B578" t="n">
@@ -14893,7 +14893,7 @@
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B579" t="n">
@@ -14918,7 +14918,7 @@
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B580" t="n">
@@ -14943,7 +14943,7 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B581" t="n">
@@ -14968,7 +14968,7 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B582" t="n">
@@ -14993,7 +14993,7 @@
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B583" t="n">
@@ -15018,7 +15018,7 @@
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B584" t="n">
@@ -15043,7 +15043,7 @@
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B585" t="n">
@@ -15068,7 +15068,7 @@
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B586" t="n">
@@ -15093,7 +15093,7 @@
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B587" t="n">
@@ -15118,7 +15118,7 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B588" t="n">
@@ -15143,7 +15143,7 @@
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B589" t="n">
@@ -15168,7 +15168,7 @@
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B590" t="n">
@@ -15193,7 +15193,7 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B591" t="n">
@@ -15218,7 +15218,7 @@
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B592" t="n">
@@ -15243,7 +15243,7 @@
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B593" t="n">
@@ -15268,7 +15268,7 @@
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B594" t="n">
@@ -15293,7 +15293,7 @@
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B595" t="n">
@@ -15318,7 +15318,7 @@
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B596" t="n">
@@ -15343,7 +15343,7 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B597" t="n">
@@ -15368,7 +15368,7 @@
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B598" t="n">
@@ -15393,7 +15393,7 @@
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B599" t="n">
@@ -15418,7 +15418,7 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B600" t="n">
@@ -15443,7 +15443,7 @@
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B601" t="n">
@@ -15468,7 +15468,7 @@
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B602" t="n">
@@ -15493,7 +15493,7 @@
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B603" t="n">
@@ -15518,7 +15518,7 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B604" t="n">
@@ -15543,7 +15543,7 @@
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B605" t="n">
@@ -15568,7 +15568,7 @@
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B606" t="n">
@@ -15593,7 +15593,7 @@
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B607" t="n">
@@ -15618,7 +15618,7 @@
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B608" t="n">
@@ -15643,7 +15643,7 @@
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B609" t="n">
@@ -15668,7 +15668,7 @@
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B610" t="n">
@@ -15693,7 +15693,7 @@
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_02.czi</t>
         </is>
       </c>
       <c r="B611" t="n">
@@ -15718,7 +15718,7 @@
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_03.czi</t>
         </is>
       </c>
       <c r="B612" t="n">
@@ -15743,7 +15743,7 @@
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_03.czi</t>
         </is>
       </c>
       <c r="B613" t="n">
@@ -15768,7 +15768,7 @@
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_03.czi</t>
         </is>
       </c>
       <c r="B614" t="n">
@@ -15793,7 +15793,7 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_03.czi</t>
         </is>
       </c>
       <c r="B615" t="n">
@@ -15818,7 +15818,7 @@
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_03.czi</t>
         </is>
       </c>
       <c r="B616" t="n">
@@ -15843,7 +15843,7 @@
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_03.czi</t>
         </is>
       </c>
       <c r="B617" t="n">
@@ -15868,7 +15868,7 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_03.czi</t>
         </is>
       </c>
       <c r="B618" t="n">
@@ -15893,7 +15893,7 @@
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_03.czi</t>
         </is>
       </c>
       <c r="B619" t="n">
@@ -15918,7 +15918,7 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_03.czi</t>
         </is>
       </c>
       <c r="B620" t="n">
@@ -15943,7 +15943,7 @@
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_03.czi</t>
         </is>
       </c>
       <c r="B621" t="n">
@@ -15968,7 +15968,7 @@
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_03.czi</t>
         </is>
       </c>
       <c r="B622" t="n">
@@ -15993,7 +15993,7 @@
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_03.czi</t>
         </is>
       </c>
       <c r="B623" t="n">
@@ -16018,7 +16018,7 @@
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_03.czi</t>
         </is>
       </c>
       <c r="B624" t="n">
@@ -16043,7 +16043,7 @@
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_03.czi</t>
         </is>
       </c>
       <c r="B625" t="n">
@@ -16068,7 +16068,7 @@
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_03.czi</t>
         </is>
       </c>
       <c r="B626" t="n">
@@ -16093,7 +16093,7 @@
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_03.czi</t>
         </is>
       </c>
       <c r="B627" t="n">
@@ -16118,7 +16118,7 @@
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_03.czi</t>
         </is>
       </c>
       <c r="B628" t="n">
@@ -16143,7 +16143,7 @@
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_03.czi</t>
         </is>
       </c>
       <c r="B629" t="n">
@@ -16168,7 +16168,7 @@
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_03.czi</t>
         </is>
       </c>
       <c r="B630" t="n">
@@ -16193,7 +16193,7 @@
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_03.czi</t>
         </is>
       </c>
       <c r="B631" t="n">
@@ -16218,7 +16218,7 @@
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_03.czi</t>
         </is>
       </c>
       <c r="B632" t="n">
@@ -16243,7 +16243,7 @@
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_03.czi</t>
         </is>
       </c>
       <c r="B633" t="n">
@@ -16268,7 +16268,7 @@
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_03.czi</t>
         </is>
       </c>
       <c r="B634" t="n">
@@ -16293,7 +16293,7 @@
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_03.czi</t>
         </is>
       </c>
       <c r="B635" t="n">
@@ -16318,7 +16318,7 @@
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_04.czi</t>
         </is>
       </c>
       <c r="B636" t="n">
@@ -16343,7 +16343,7 @@
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_04.czi</t>
         </is>
       </c>
       <c r="B637" t="n">
@@ -16368,7 +16368,7 @@
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_04.czi</t>
         </is>
       </c>
       <c r="B638" t="n">
@@ -16393,7 +16393,7 @@
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_04.czi</t>
         </is>
       </c>
       <c r="B639" t="n">
@@ -16418,7 +16418,7 @@
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_04.czi</t>
         </is>
       </c>
       <c r="B640" t="n">
@@ -16443,7 +16443,7 @@
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_04.czi</t>
         </is>
       </c>
       <c r="B641" t="n">
@@ -16468,7 +16468,7 @@
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_04.czi</t>
         </is>
       </c>
       <c r="B642" t="n">
@@ -16493,7 +16493,7 @@
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_04.czi</t>
         </is>
       </c>
       <c r="B643" t="n">
@@ -16518,7 +16518,7 @@
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_04.czi</t>
         </is>
       </c>
       <c r="B644" t="n">
@@ -16543,7 +16543,7 @@
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_04.czi</t>
         </is>
       </c>
       <c r="B645" t="n">
@@ -16568,7 +16568,7 @@
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_04.czi</t>
         </is>
       </c>
       <c r="B646" t="n">
@@ -16593,7 +16593,7 @@
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_04.czi</t>
         </is>
       </c>
       <c r="B647" t="n">
@@ -16618,7 +16618,7 @@
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_04.czi</t>
         </is>
       </c>
       <c r="B648" t="n">
@@ -16643,7 +16643,7 @@
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_04.czi</t>
         </is>
       </c>
       <c r="B649" t="n">
@@ -16668,7 +16668,7 @@
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_04.czi</t>
         </is>
       </c>
       <c r="B650" t="n">
@@ -16693,7 +16693,7 @@
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_04.czi</t>
         </is>
       </c>
       <c r="B651" t="n">
@@ -16718,7 +16718,7 @@
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_04.czi</t>
         </is>
       </c>
       <c r="B652" t="n">
@@ -16743,7 +16743,7 @@
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_04.czi</t>
         </is>
       </c>
       <c r="B653" t="n">
@@ -16768,7 +16768,7 @@
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_04.czi</t>
         </is>
       </c>
       <c r="B654" t="n">
@@ -16793,7 +16793,7 @@
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_04.czi</t>
         </is>
       </c>
       <c r="B655" t="n">
@@ -16818,7 +16818,7 @@
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_04.czi</t>
         </is>
       </c>
       <c r="B656" t="n">
@@ -16843,7 +16843,7 @@
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_04.czi</t>
         </is>
       </c>
       <c r="B657" t="n">
@@ -16868,7 +16868,7 @@
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_04.czi</t>
         </is>
       </c>
       <c r="B658" t="n">
@@ -16893,7 +16893,7 @@
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_04.czi</t>
         </is>
       </c>
       <c r="B659" t="n">
@@ -16918,7 +16918,7 @@
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_04.czi</t>
         </is>
       </c>
       <c r="B660" t="n">
@@ -16943,7 +16943,7 @@
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_04.czi</t>
         </is>
       </c>
       <c r="B661" t="n">
@@ -16968,7 +16968,7 @@
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_04.czi</t>
         </is>
       </c>
       <c r="B662" t="n">
@@ -16993,7 +16993,7 @@
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_04.czi</t>
         </is>
       </c>
       <c r="B663" t="n">
@@ -17018,7 +17018,7 @@
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_04.czi</t>
         </is>
       </c>
       <c r="B664" t="n">
@@ -17043,7 +17043,7 @@
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_04.czi</t>
         </is>
       </c>
       <c r="B665" t="n">
@@ -17068,7 +17068,7 @@
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_04.czi</t>
         </is>
       </c>
       <c r="B666" t="n">
@@ -17093,7 +17093,7 @@
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_04.czi</t>
         </is>
       </c>
       <c r="B667" t="n">
@@ -17118,7 +17118,7 @@
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_04.czi</t>
         </is>
       </c>
       <c r="B668" t="n">
@@ -17143,7 +17143,7 @@
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_04.czi</t>
         </is>
       </c>
       <c r="B669" t="n">
@@ -17168,7 +17168,7 @@
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_04.czi</t>
         </is>
       </c>
       <c r="B670" t="n">
@@ -17193,7 +17193,7 @@
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_04.czi</t>
         </is>
       </c>
       <c r="B671" t="n">
@@ -17218,7 +17218,7 @@
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_04.czi</t>
         </is>
       </c>
       <c r="B672" t="n">
@@ -17243,7 +17243,7 @@
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_04.czi</t>
         </is>
       </c>
       <c r="B673" t="n">
@@ -17268,7 +17268,7 @@
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_04.czi</t>
         </is>
       </c>
       <c r="B674" t="n">
@@ -17293,7 +17293,7 @@
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_04.czi</t>
         </is>
       </c>
       <c r="B675" t="n">
@@ -17318,7 +17318,7 @@
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_04.czi</t>
         </is>
       </c>
       <c r="B676" t="n">
@@ -17343,7 +17343,7 @@
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_04.czi</t>
         </is>
       </c>
       <c r="B677" t="n">
@@ -17368,7 +17368,7 @@
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_04.czi</t>
         </is>
       </c>
       <c r="B678" t="n">
@@ -17393,7 +17393,7 @@
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B679" t="n">
@@ -17418,7 +17418,7 @@
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B680" t="n">
@@ -17443,7 +17443,7 @@
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B681" t="n">
@@ -17468,7 +17468,7 @@
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B682" t="n">
@@ -17493,7 +17493,7 @@
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B683" t="n">
@@ -17518,7 +17518,7 @@
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B684" t="n">
@@ -17543,7 +17543,7 @@
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B685" t="n">
@@ -17568,7 +17568,7 @@
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B686" t="n">
@@ -17593,7 +17593,7 @@
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B687" t="n">
@@ -17618,7 +17618,7 @@
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B688" t="n">
@@ -17643,7 +17643,7 @@
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B689" t="n">
@@ -17668,7 +17668,7 @@
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B690" t="n">
@@ -17693,7 +17693,7 @@
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B691" t="n">
@@ -17718,7 +17718,7 @@
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B692" t="n">
@@ -17743,7 +17743,7 @@
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B693" t="n">
@@ -17768,7 +17768,7 @@
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B694" t="n">
@@ -17793,7 +17793,7 @@
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B695" t="n">
@@ -17818,7 +17818,7 @@
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B696" t="n">
@@ -17843,7 +17843,7 @@
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B697" t="n">
@@ -17868,7 +17868,7 @@
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B698" t="n">
@@ -17893,7 +17893,7 @@
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B699" t="n">
@@ -17918,7 +17918,7 @@
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B700" t="n">
@@ -17943,7 +17943,7 @@
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B701" t="n">
@@ -17968,7 +17968,7 @@
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B702" t="n">
@@ -17993,7 +17993,7 @@
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B703" t="n">
@@ -18018,7 +18018,7 @@
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B704" t="n">
@@ -18043,7 +18043,7 @@
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B705" t="n">
@@ -18068,7 +18068,7 @@
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B706" t="n">
@@ -18093,7 +18093,7 @@
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B707" t="n">
@@ -18118,7 +18118,7 @@
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B708" t="n">
@@ -18143,7 +18143,7 @@
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B709" t="n">
@@ -18168,7 +18168,7 @@
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B710" t="n">
@@ -18193,7 +18193,7 @@
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B711" t="n">
@@ -18218,7 +18218,7 @@
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B712" t="n">
@@ -18243,7 +18243,7 @@
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B713" t="n">
@@ -18268,7 +18268,7 @@
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B714" t="n">
@@ -18293,7 +18293,7 @@
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B715" t="n">
@@ -18318,7 +18318,7 @@
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B716" t="n">
@@ -18343,7 +18343,7 @@
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B717" t="n">
@@ -18368,7 +18368,7 @@
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B718" t="n">
@@ -18393,7 +18393,7 @@
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B719" t="n">
@@ -18418,7 +18418,7 @@
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B720" t="n">
@@ -18443,7 +18443,7 @@
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B721" t="n">
@@ -18468,7 +18468,7 @@
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B722" t="n">
@@ -18493,7 +18493,7 @@
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B723" t="n">
@@ -18518,7 +18518,7 @@
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B724" t="n">
@@ -18543,7 +18543,7 @@
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B725" t="n">
@@ -18568,7 +18568,7 @@
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B726" t="n">
@@ -18593,7 +18593,7 @@
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B727" t="n">
@@ -18618,7 +18618,7 @@
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B728" t="n">
@@ -18643,7 +18643,7 @@
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B729" t="n">
@@ -18668,7 +18668,7 @@
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B730" t="n">
@@ -18693,7 +18693,7 @@
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B731" t="n">
@@ -18718,7 +18718,7 @@
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_05.czi</t>
         </is>
       </c>
       <c r="B732" t="n">
@@ -18743,7 +18743,7 @@
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_06.czi</t>
         </is>
       </c>
       <c r="B733" t="n">
@@ -18768,7 +18768,7 @@
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_06.czi</t>
         </is>
       </c>
       <c r="B734" t="n">
@@ -18793,7 +18793,7 @@
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_06.czi</t>
         </is>
       </c>
       <c r="B735" t="n">
@@ -18818,7 +18818,7 @@
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_06.czi</t>
         </is>
       </c>
       <c r="B736" t="n">
@@ -18843,7 +18843,7 @@
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_06.czi</t>
         </is>
       </c>
       <c r="B737" t="n">
@@ -18868,7 +18868,7 @@
     <row r="738">
       <c r="A738" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_06.czi</t>
         </is>
       </c>
       <c r="B738" t="n">
@@ -18893,7 +18893,7 @@
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_06.czi</t>
         </is>
       </c>
       <c r="B739" t="n">
@@ -18918,7 +18918,7 @@
     <row r="740">
       <c r="A740" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_06.czi</t>
         </is>
       </c>
       <c r="B740" t="n">
@@ -18943,7 +18943,7 @@
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_06.czi</t>
         </is>
       </c>
       <c r="B741" t="n">
@@ -18968,7 +18968,7 @@
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_06.czi</t>
         </is>
       </c>
       <c r="B742" t="n">
@@ -18993,7 +18993,7 @@
     <row r="743">
       <c r="A743" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_06.czi</t>
         </is>
       </c>
       <c r="B743" t="n">
@@ -19018,7 +19018,7 @@
     <row r="744">
       <c r="A744" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_06.czi</t>
         </is>
       </c>
       <c r="B744" t="n">
@@ -19043,7 +19043,7 @@
     <row r="745">
       <c r="A745" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_06.czi</t>
         </is>
       </c>
       <c r="B745" t="n">
@@ -19068,7 +19068,7 @@
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_06.czi</t>
         </is>
       </c>
       <c r="B746" t="n">
@@ -19093,7 +19093,7 @@
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_06.czi</t>
         </is>
       </c>
       <c r="B747" t="n">
@@ -19118,7 +19118,7 @@
     <row r="748">
       <c r="A748" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_06.czi</t>
         </is>
       </c>
       <c r="B748" t="n">
@@ -19143,7 +19143,7 @@
     <row r="749">
       <c r="A749" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_06.czi</t>
         </is>
       </c>
       <c r="B749" t="n">
@@ -19168,7 +19168,7 @@
     <row r="750">
       <c r="A750" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_06.czi</t>
         </is>
       </c>
       <c r="B750" t="n">
@@ -19193,7 +19193,7 @@
     <row r="751">
       <c r="A751" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_06.czi</t>
         </is>
       </c>
       <c r="B751" t="n">
@@ -19218,7 +19218,7 @@
     <row r="752">
       <c r="A752" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_06.czi</t>
         </is>
       </c>
       <c r="B752" t="n">
@@ -19243,7 +19243,7 @@
     <row r="753">
       <c r="A753" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_06.czi</t>
         </is>
       </c>
       <c r="B753" t="n">
@@ -19268,7 +19268,7 @@
     <row r="754">
       <c r="A754" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_06.czi</t>
         </is>
       </c>
       <c r="B754" t="n">
@@ -19293,7 +19293,7 @@
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_06.czi</t>
         </is>
       </c>
       <c r="B755" t="n">
@@ -19318,7 +19318,7 @@
     <row r="756">
       <c r="A756" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_06.czi</t>
         </is>
       </c>
       <c r="B756" t="n">
@@ -19343,7 +19343,7 @@
     <row r="757">
       <c r="A757" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_06.czi</t>
         </is>
       </c>
       <c r="B757" t="n">
@@ -19368,7 +19368,7 @@
     <row r="758">
       <c r="A758" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_06.czi</t>
         </is>
       </c>
       <c r="B758" t="n">
@@ -19393,7 +19393,7 @@
     <row r="759">
       <c r="A759" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_06.czi</t>
         </is>
       </c>
       <c r="B759" t="n">
@@ -19418,7 +19418,7 @@
     <row r="760">
       <c r="A760" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_06.czi</t>
         </is>
       </c>
       <c r="B760" t="n">
@@ -19443,7 +19443,7 @@
     <row r="761">
       <c r="A761" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_06.czi</t>
         </is>
       </c>
       <c r="B761" t="n">
@@ -19468,7 +19468,7 @@
     <row r="762">
       <c r="A762" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_06.czi</t>
         </is>
       </c>
       <c r="B762" t="n">
@@ -19493,7 +19493,7 @@
     <row r="763">
       <c r="A763" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_06.czi</t>
         </is>
       </c>
       <c r="B763" t="n">
@@ -19518,7 +19518,7 @@
     <row r="764">
       <c r="A764" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_06.czi</t>
         </is>
       </c>
       <c r="B764" t="n">
@@ -19543,7 +19543,7 @@
     <row r="765">
       <c r="A765" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_06.czi</t>
         </is>
       </c>
       <c r="B765" t="n">
@@ -19568,7 +19568,7 @@
     <row r="766">
       <c r="A766" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_06.czi</t>
         </is>
       </c>
       <c r="B766" t="n">
@@ -19593,7 +19593,7 @@
     <row r="767">
       <c r="A767" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_06.czi</t>
         </is>
       </c>
       <c r="B767" t="n">
@@ -19618,7 +19618,7 @@
     <row r="768">
       <c r="A768" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_06.czi</t>
         </is>
       </c>
       <c r="B768" t="n">
@@ -19643,7 +19643,7 @@
     <row r="769">
       <c r="A769" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_06.czi</t>
         </is>
       </c>
       <c r="B769" t="n">
@@ -19668,7 +19668,7 @@
     <row r="770">
       <c r="A770" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_06.czi</t>
         </is>
       </c>
       <c r="B770" t="n">
@@ -19693,7 +19693,7 @@
     <row r="771">
       <c r="A771" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_06.czi</t>
         </is>
       </c>
       <c r="B771" t="n">
@@ -19718,7 +19718,7 @@
     <row r="772">
       <c r="A772" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_06.czi</t>
         </is>
       </c>
       <c r="B772" t="n">
@@ -19743,7 +19743,7 @@
     <row r="773">
       <c r="A773" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_06.czi</t>
         </is>
       </c>
       <c r="B773" t="n">
@@ -19768,7 +19768,7 @@
     <row r="774">
       <c r="A774" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_06.czi</t>
         </is>
       </c>
       <c r="B774" t="n">
@@ -19793,7 +19793,7 @@
     <row r="775">
       <c r="A775" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_06.czi</t>
         </is>
       </c>
       <c r="B775" t="n">
@@ -19818,7 +19818,7 @@
     <row r="776">
       <c r="A776" t="inlineStr">
         <is>
-          <t>12225_SUMMARY.xlsx</t>
+          <t>12225_images\3K_C12_OA_24h_LT_06.czi</t>
         </is>
       </c>
       <c r="B776" t="n">
